--- a/Procurement Dependent Fields.xlsx
+++ b/Procurement Dependent Fields.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://horizontal-my.sharepoint.com/personal/dpanchal_horizontal_com/Documents/CursorAutomation/ProcurementClassification/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="11_F25DC773A252ABDACC104832F11D406A5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAA688C0-674F-4E08-948B-6A457020ABDE}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="11_F25DC773A252ABDACC104832F11D406A5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B398A8C-A5BD-4102-9F4F-D8B69497AC5E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="11475" yWindow="-15420" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -130,10 +130,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -422,87 +422,88 @@
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="4"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
       <c r="C4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
       <c r="C7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
       <c r="C9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
